--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487116_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487116_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.48</v>
+        <v>4.6133</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8071</v>
+        <v>5.6459</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.3271</v>
+        <v>-1.0326</v>
       </c>
       <c r="G2" t="n">
         <v>6.6283</v>
@@ -610,13 +610,13 @@
         <v>1.7371</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.6089</v>
+        <v>-1.4757</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.2056</v>
+        <v>-0.3668</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.4033</v>
+        <v>-1.1089</v>
       </c>
       <c r="V2" t="n">
         <v>2.7418</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3165</v>
+        <v>2.842</v>
       </c>
       <c r="E3" t="n">
-        <v>2.7146</v>
+        <v>3.2937</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3981</v>
+        <v>-0.4517</v>
       </c>
       <c r="G3" t="n">
         <v>3.84</v>
@@ -688,13 +688,13 @@
         <v>1.5441</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.4886</v>
+        <v>-0.9631</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0126</v>
+        <v>-0.4336</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.476</v>
+        <v>-0.5295</v>
       </c>
       <c r="V3" t="n">
         <v>-0.614</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>O. HERNANDEZ HERNANDEZ</t>
+          <t>J. OTERO GONZALEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8554</v>
+        <v>0.6994</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1581</v>
+        <v>0.9762</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3028</v>
+        <v>-0.2768</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8018</v>
+        <v>1.2752</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7183</v>
+        <v>2.8089</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0835</v>
+        <v>-1.5337</v>
       </c>
       <c r="J4" t="n">
-        <v>2.416</v>
+        <v>2.8626</v>
       </c>
       <c r="K4" t="n">
-        <v>1.4799</v>
+        <v>3.2703</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9361</v>
+        <v>-0.4077</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.6141</v>
+        <v>-1.5873</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7616000000000001</v>
+        <v>-0.4613</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8526</v>
+        <v>-1.126</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.772</v>
+        <v>-0.579</v>
       </c>
       <c r="Q4" t="n">
         <v>-2.1231</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3511</v>
+        <v>1.5441</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3973</v>
+        <v>-0.6108</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2935</v>
+        <v>-0.0069</v>
       </c>
       <c r="U4" t="n">
-        <v>1.1038</v>
+        <v>-0.6039</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.5717</v>
+        <v>0.614</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5717</v>
+        <v>0.2436</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.1435</v>
+        <v>0.3704</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. REYES ABAD</t>
+          <t>O. HERNANDEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4008</v>
+        <v>0.0979</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6749</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.2741</v>
+        <v>-0.8381</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.2235</v>
+        <v>0.8018</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8168</v>
+        <v>0.7183</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.0403</v>
+        <v>0.0835</v>
       </c>
       <c r="J5" t="n">
-        <v>1.4973</v>
+        <v>2.416</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2781</v>
+        <v>1.4799</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2192</v>
+        <v>0.9361</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.7209</v>
+        <v>-1.6141</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4613</v>
+        <v>-0.7616000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.2596</v>
+        <v>-0.8526</v>
       </c>
       <c r="P5" t="n">
-        <v>0.579</v>
+        <v>-0.772</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.965</v>
+        <v>-2.1231</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5441</v>
+        <v>1.3511</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2406</v>
+        <v>0.6398</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8567</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.0973</v>
+        <v>0.5684</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2859</v>
+        <v>-0.5717</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2859</v>
+        <v>0.5717</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.1435</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. OTERO GONZALEZ</t>
+          <t>E. CARPINTERO REVILLA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2215</v>
+        <v>-0.0564</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5786</v>
+        <v>-1.3067</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3571</v>
+        <v>1.2502</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2752</v>
+        <v>0.6948</v>
       </c>
       <c r="H6" t="n">
-        <v>2.8089</v>
+        <v>0.532</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.5337</v>
+        <v>0.1628</v>
       </c>
       <c r="J6" t="n">
-        <v>2.8626</v>
+        <v>-0.1995</v>
       </c>
       <c r="K6" t="n">
-        <v>3.2703</v>
+        <v>0.3053</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.4077</v>
+        <v>-0.5048</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.5873</v>
+        <v>0.8944</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4613</v>
+        <v>0.2268</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.126</v>
+        <v>0.6676</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.579</v>
+        <v>-0.386</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.1231</v>
+        <v>-1.158</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5441</v>
+        <v>0.772</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0887</v>
+        <v>-0.4075</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4045</v>
+        <v>0.0509</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6842</v>
+        <v>-0.4584</v>
       </c>
       <c r="V6" t="n">
-        <v>0.614</v>
+        <v>0.0422</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2436</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3704</v>
+        <v>0.0422</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. CARPINTERO REVILLA</t>
+          <t>A. REYES ABAD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2894</v>
+        <v>-0.3557</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.5665</v>
+        <v>0.8113</v>
       </c>
       <c r="F7" t="n">
-        <v>1.277</v>
+        <v>-1.167</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6948</v>
+        <v>-0.2235</v>
       </c>
       <c r="H7" t="n">
-        <v>0.532</v>
+        <v>0.8168</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1628</v>
+        <v>-1.0403</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1995</v>
+        <v>1.4973</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3053</v>
+        <v>1.2781</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5048</v>
+        <v>0.2192</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8944</v>
+        <v>-1.7209</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2268</v>
+        <v>-0.4613</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6676</v>
+        <v>-1.2596</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.386</v>
+        <v>0.579</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.158</v>
+        <v>-0.965</v>
       </c>
       <c r="R7" t="n">
-        <v>0.772</v>
+        <v>1.5441</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6405</v>
+        <v>-0.9971</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2089</v>
+        <v>-0.0069</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4316</v>
+        <v>-0.9902</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0422</v>
+        <v>0.2859</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0422</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9604</v>
+        <v>-0.7611</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0818</v>
+        <v>0.0372</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8786</v>
+        <v>-0.7983</v>
       </c>
       <c r="G8" t="n">
         <v>0.2558</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6445</v>
+        <v>-0.4452</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1639</v>
+        <v>-0.0449</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4805</v>
+        <v>-0.4002</v>
       </c>
       <c r="V8" t="n">
         <v>-0.5717</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3787</v>
+        <v>-1.2121</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0038</v>
+        <v>-0.9443</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3748</v>
+        <v>-0.2678</v>
       </c>
       <c r="G9" t="n">
         <v>-0.4067</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4931</v>
+        <v>-0.3265</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1639</v>
+        <v>-0.1044</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3292</v>
+        <v>-0.2221</v>
       </c>
       <c r="V9" t="n">
         <v>-0.2859</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.5679</v>
+        <v>-1.3021</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8092</v>
+        <v>-1.4899</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2413</v>
+        <v>0.1878</v>
       </c>
       <c r="G10" t="n">
         <v>-0.8196</v>
@@ -1234,13 +1234,13 @@
         <v>0.193</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0238</v>
+        <v>0.2895</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.238</v>
+        <v>0.0813</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2617</v>
+        <v>0.2082</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,40 +1267,40 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>3.0778</v>
+        <v>4.565199999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>6.472000000000002</v>
+        <v>7.9594</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.3943</v>
+        <v>-3.394299999999999</v>
       </c>
       <c r="G11" t="n">
         <v>12.0461</v>
       </c>
       <c r="H11" t="n">
-        <v>4.606000000000001</v>
+        <v>4.606</v>
       </c>
       <c r="I11" t="n">
-        <v>7.44</v>
+        <v>7.439999999999999</v>
       </c>
       <c r="J11" t="n">
         <v>18.7149</v>
       </c>
       <c r="K11" t="n">
-        <v>6.979799999999999</v>
+        <v>6.9798</v>
       </c>
       <c r="L11" t="n">
         <v>11.7351</v>
       </c>
       <c r="M11" t="n">
-        <v>-6.6685</v>
+        <v>-6.668500000000001</v>
       </c>
       <c r="N11" t="n">
         <v>-2.3737</v>
       </c>
       <c r="O11" t="n">
-        <v>-4.295100000000001</v>
+        <v>-4.2951</v>
       </c>
       <c r="P11" t="n">
         <v>-4.8251</v>
@@ -1312,10 +1312,10 @@
         <v>8.685499999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>-5.783800000000001</v>
+        <v>-4.2966</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.2472</v>
+        <v>-0.7599</v>
       </c>
       <c r="U11" t="n">
         <v>-3.5366</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>8.893000000000001</v>
+        <v>7.2895</v>
       </c>
       <c r="E12" t="n">
-        <v>6.0847</v>
+        <v>4.4824</v>
       </c>
       <c r="F12" t="n">
-        <v>2.8083</v>
+        <v>2.807</v>
       </c>
       <c r="G12" t="n">
         <v>1.4088</v>
@@ -1390,13 +1390,13 @@
         <v>2.5091</v>
       </c>
       <c r="S12" t="n">
-        <v>4.8384</v>
+        <v>3.2349</v>
       </c>
       <c r="T12" t="n">
-        <v>3.498</v>
+        <v>1.8958</v>
       </c>
       <c r="U12" t="n">
-        <v>1.3404</v>
+        <v>1.3391</v>
       </c>
       <c r="V12" t="n">
         <v>2.0667</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>I. SALAZAR ORTEGA</t>
+          <t>I. BETOLAZA BELOKI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.913</v>
+        <v>2.8509</v>
       </c>
       <c r="E13" t="n">
-        <v>4.5445</v>
+        <v>6.2453</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3685</v>
+        <v>-3.3944</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.2241</v>
+        <v>2.3831</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2732</v>
+        <v>-1.1498</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.4973</v>
+        <v>3.533</v>
       </c>
       <c r="J13" t="n">
-        <v>2.0115</v>
+        <v>6.6468</v>
       </c>
       <c r="K13" t="n">
-        <v>1.0347</v>
+        <v>0.2327</v>
       </c>
       <c r="L13" t="n">
-        <v>0.9768</v>
+        <v>6.4141</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.2357</v>
+        <v>-4.2636</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.7616000000000001</v>
+        <v>-1.3825</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.4741</v>
+        <v>-2.8811</v>
       </c>
       <c r="P13" t="n">
-        <v>2.1231</v>
+        <v>1.158</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R13" t="n">
         <v>2.1231</v>
       </c>
       <c r="S13" t="n">
-        <v>4.2343</v>
+        <v>1.086</v>
       </c>
       <c r="T13" t="n">
-        <v>2.533</v>
+        <v>0.5635</v>
       </c>
       <c r="U13" t="n">
-        <v>1.7013</v>
+        <v>0.5225</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.2202</v>
+        <v>-1.7763</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.2202</v>
+        <v>-1.7763</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>I. BETOLAZA BELOKI</t>
+          <t>I. SALAZAR ORTEGA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.4549</v>
+        <v>2.8011</v>
       </c>
       <c r="E14" t="n">
-        <v>5.5443</v>
+        <v>2.9422</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.0894</v>
+        <v>-0.1411</v>
       </c>
       <c r="G14" t="n">
-        <v>2.3831</v>
+        <v>-1.2241</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.1498</v>
+        <v>0.2732</v>
       </c>
       <c r="I14" t="n">
-        <v>3.533</v>
+        <v>-1.4973</v>
       </c>
       <c r="J14" t="n">
-        <v>6.6468</v>
+        <v>2.0115</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2327</v>
+        <v>1.0347</v>
       </c>
       <c r="L14" t="n">
-        <v>6.4141</v>
+        <v>0.9768</v>
       </c>
       <c r="M14" t="n">
-        <v>-4.2636</v>
+        <v>-3.2357</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.3825</v>
+        <v>-0.7616000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.8811</v>
+        <v>-2.4741</v>
       </c>
       <c r="P14" t="n">
-        <v>1.158</v>
+        <v>2.1231</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>2.1231</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.31</v>
+        <v>2.1224</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1374</v>
+        <v>0.9307</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1725</v>
+        <v>1.1917</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.7763</v>
+        <v>-0.2202</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.7763</v>
+        <v>-0.2202</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1166</v>
+        <v>0.0566</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.63</v>
+        <v>-1.4298</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5135</v>
+        <v>1.4864</v>
       </c>
       <c r="G15" t="n">
         <v>-0.7524</v>
@@ -1624,13 +1624,13 @@
         <v>0.579</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0568</v>
+        <v>0.23</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3569</v>
+        <v>-0.1566</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4138</v>
+        <v>0.3867</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.476</v>
+        <v>0.0115</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.4916</v>
+        <v>-0.1911</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0156</v>
+        <v>0.2026</v>
       </c>
       <c r="G16" t="n">
         <v>-0.821</v>
@@ -1702,13 +1702,13 @@
         <v>0.579</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2763</v>
+        <v>0.2112</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.238</v>
+        <v>0.0625</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0383</v>
+        <v>0.1487</v>
       </c>
       <c r="V16" t="n">
         <v>0.0422</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.8246</v>
+        <v>-0.4571</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.9837</v>
+        <v>-0.8835</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1591</v>
+        <v>0.4265</v>
       </c>
       <c r="G17" t="n">
         <v>1.0424</v>
@@ -1780,13 +1780,13 @@
         <v>0.772</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9948</v>
+        <v>-0.6273</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6544</v>
+        <v>-0.5542</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3404</v>
+        <v>-0.0731</v>
       </c>
       <c r="V17" t="n">
         <v>0.2859</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.9452</v>
+        <v>-1.577</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7793</v>
+        <v>0.4788</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.7244</v>
+        <v>-2.0558</v>
       </c>
       <c r="G18" t="n">
         <v>-3.0389</v>
@@ -1858,13 +1858,13 @@
         <v>1.9301</v>
       </c>
       <c r="S18" t="n">
-        <v>1.3332</v>
+        <v>1.7014</v>
       </c>
       <c r="T18" t="n">
-        <v>1.3167</v>
+        <v>1.0163</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0165</v>
+        <v>0.6851</v>
       </c>
       <c r="V18" t="n">
         <v>-1.2046</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. MENDIA SANGRONIZ</t>
+          <t>E. SALINERO GARCIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.3184</v>
+        <v>-2.4518</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2594</v>
+        <v>-2.2496</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.059</v>
+        <v>-0.2022</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.2971</v>
+        <v>-3.2665</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5568</v>
+        <v>-1.6364</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.8539</v>
+        <v>-1.6301</v>
       </c>
       <c r="J19" t="n">
-        <v>0.479</v>
+        <v>-1.9393</v>
       </c>
       <c r="K19" t="n">
-        <v>1.6921</v>
+        <v>-1.8165</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.2131</v>
+        <v>-0.1228</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.7761</v>
+        <v>-1.3272</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1353</v>
+        <v>0.1801</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.6408</v>
+        <v>-1.5073</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.193</v>
+        <v>0.965</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.965</v>
       </c>
       <c r="R19" t="n">
-        <v>0.772</v>
+        <v>1.9301</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8705000000000001</v>
+        <v>0.7261</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7733</v>
+        <v>0.3689</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.09719999999999999</v>
+        <v>0.3573</v>
       </c>
       <c r="V19" t="n">
-        <v>0.0422</v>
+        <v>-0.8764999999999999</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X19" t="n">
-        <v>0.0422</v>
+        <v>-1.1623</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. ERRASTI DIEZ</t>
+          <t>B. MENDIA SANGRONIZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.5764</v>
+        <v>-2.4968</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.5975</v>
+        <v>-0.7587</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.9788</v>
+        <v>-1.7381</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.9788</v>
+        <v>-2.2971</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.6332</v>
+        <v>0.5568</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3456</v>
+        <v>-2.8539</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.09710000000000001</v>
+        <v>0.479</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.2524</v>
+        <v>1.6921</v>
       </c>
       <c r="L20" t="n">
-        <v>1.1553</v>
+        <v>-1.2131</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.8817</v>
+        <v>-2.7761</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3808</v>
+        <v>-1.1353</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.5009</v>
+        <v>-1.6408</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.772</v>
+        <v>-0.193</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.965</v>
       </c>
       <c r="R20" t="n">
-        <v>0.193</v>
+        <v>0.772</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8256</v>
+        <v>-0.0489</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5354</v>
+        <v>-0.2726</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2902</v>
+        <v>0.2237</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.0422</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.0422</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. PEREZ BENITO</t>
+          <t>E. ERRASTI DIEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.8667</v>
+        <v>-3.0552</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.145</v>
+        <v>-1.3972</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2783</v>
+        <v>-1.6579</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.5018</v>
+        <v>-1.9788</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.0491</v>
+        <v>-1.6332</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4527</v>
+        <v>-0.3456</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.8621</v>
+        <v>-0.09710000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.6083</v>
+        <v>-1.2524</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.2538</v>
+        <v>1.1553</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3603</v>
+        <v>-1.8817</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4408</v>
+        <v>-0.3808</v>
       </c>
       <c r="O21" t="n">
-        <v>0.8011</v>
+        <v>-1.5009</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-0.772</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>0.193</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3649</v>
+        <v>-0.3044</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2829</v>
+        <v>-0.3351</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.082</v>
+        <v>0.0307</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E. SALINERO GARCIA</t>
+          <t>J. PEREZ BENITO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.215</v>
+        <v>-3.3792</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.4513</v>
+        <v>-3.8446</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7637</v>
+        <v>0.4654</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.2665</v>
+        <v>-3.5018</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.6364</v>
+        <v>-3.0491</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.6301</v>
+        <v>-0.4527</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.9393</v>
+        <v>-3.8621</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.8165</v>
+        <v>-2.6083</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.1228</v>
+        <v>-1.2538</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.3272</v>
+        <v>0.3603</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1801</v>
+        <v>-0.4408</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.5073</v>
+        <v>0.8011</v>
       </c>
       <c r="P22" t="n">
-        <v>0.965</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.9301</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0371</v>
+        <v>0.1226</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8328</v>
+        <v>0.0175</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2043</v>
+        <v>0.1051</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.8764999999999999</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.1623</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.077999999999998</v>
+        <v>-0.4075000000000024</v>
       </c>
       <c r="E23" t="n">
-        <v>3.394300000000001</v>
+        <v>3.394200000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-6.472000000000001</v>
+        <v>-3.801600000000001</v>
       </c>
       <c r="G23" t="n">
         <v>-12.0463</v>
@@ -2221,10 +2221,10 @@
         <v>-7.440200000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>6.6687</v>
+        <v>6.668699999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>2.373699999999999</v>
+        <v>2.3737</v>
       </c>
       <c r="L23" t="n">
         <v>4.295000000000002</v>
@@ -2239,7 +2239,7 @@
         <v>-11.7351</v>
       </c>
       <c r="P23" t="n">
-        <v>4.825099999999999</v>
+        <v>4.8251</v>
       </c>
       <c r="Q23" t="n">
         <v>-8.6852</v>
@@ -2248,13 +2248,13 @@
         <v>13.5105</v>
       </c>
       <c r="S23" t="n">
-        <v>5.783500000000001</v>
+        <v>8.454000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>3.536600000000001</v>
+        <v>3.536699999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>2.2471</v>
+        <v>4.9175</v>
       </c>
       <c r="V23" t="n">
         <v>-1.6406</v>
